--- a/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_1/labeling.xlsx
+++ b/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_1/labeling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/m_penuela_cgiar_org/Documents/Documents/projects/lmf/data/data_organization_june/subset_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72EB6427-8739-4CA4-9517-6A8B98942528}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9711E8D5-AA57-48AD-99FD-BC6032C61B89}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-8270" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="210">
   <si>
     <t>40n_no</t>
   </si>
@@ -370,6 +370,291 @@
   </si>
   <si>
     <t>40g_result_gp_data_vf</t>
+  </si>
+  <si>
+    <t>32_no</t>
+  </si>
+  <si>
+    <t>32_date</t>
+  </si>
+  <si>
+    <t>32_gene_bank_id</t>
+  </si>
+  <si>
+    <t>32_name</t>
+  </si>
+  <si>
+    <t>32_ciat_id</t>
+  </si>
+  <si>
+    <t>32_set_ciat</t>
+  </si>
+  <si>
+    <t>32_batch</t>
+  </si>
+  <si>
+    <t>32_run</t>
+  </si>
+  <si>
+    <t>32_replication</t>
+  </si>
+  <si>
+    <t>32_syrange_no</t>
+  </si>
+  <si>
+    <t>32_bag_weight_g</t>
+  </si>
+  <si>
+    <t>32_digested_weight_g</t>
+  </si>
+  <si>
+    <t>32_remarks_1</t>
+  </si>
+  <si>
+    <t>32_undigested_dm_g</t>
+  </si>
+  <si>
+    <t>32_digested_feed_mg</t>
+  </si>
+  <si>
+    <t>32_percentage_dmd_truly_digestibility</t>
+  </si>
+  <si>
+    <t>32_ndf_incubated_mg</t>
+  </si>
+  <si>
+    <t>32_ndf_digestibility_mg</t>
+  </si>
+  <si>
+    <t>32_percentage_ndf_digestibility_in_24h</t>
+  </si>
+  <si>
+    <t>32_remarks_2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Syrange No</t>
+  </si>
+  <si>
+    <t>Bag weight, g</t>
+  </si>
+  <si>
+    <t>Digested weight, g</t>
+  </si>
+  <si>
+    <t>Undigested DM, g</t>
+  </si>
+  <si>
+    <t>Digested feed, mg</t>
+  </si>
+  <si>
+    <t>NDF incubated, mg</t>
+  </si>
+  <si>
+    <t>NDF digestibility, mg</t>
+  </si>
+  <si>
+    <t>% NDF digestibility in 24 h</t>
+  </si>
+  <si>
+    <t>32_digest</t>
+  </si>
+  <si>
+    <t>31_no</t>
+  </si>
+  <si>
+    <t>31_date</t>
+  </si>
+  <si>
+    <t>31_requisitioner</t>
+  </si>
+  <si>
+    <t>31_gene_bank_id</t>
+  </si>
+  <si>
+    <t>31_genus</t>
+  </si>
+  <si>
+    <t>31_species</t>
+  </si>
+  <si>
+    <t>31_tax_name</t>
+  </si>
+  <si>
+    <t>31_family</t>
+  </si>
+  <si>
+    <t>31_order</t>
+  </si>
+  <si>
+    <t>31_functional_group</t>
+  </si>
+  <si>
+    <t>31_ciat_id</t>
+  </si>
+  <si>
+    <t>31_set_ciat</t>
+  </si>
+  <si>
+    <t>31_batch</t>
+  </si>
+  <si>
+    <t>31_run</t>
+  </si>
+  <si>
+    <t>31_replication</t>
+  </si>
+  <si>
+    <t>31_syrange_no</t>
+  </si>
+  <si>
+    <t>31_sample_weight_g</t>
+  </si>
+  <si>
+    <t>31_dm_incubated_mg</t>
+  </si>
+  <si>
+    <t>31_digested_feed_mg</t>
+  </si>
+  <si>
+    <t>31_time_0h</t>
+  </si>
+  <si>
+    <t>31_gas_0h_ml</t>
+  </si>
+  <si>
+    <t>31_time_8h</t>
+  </si>
+  <si>
+    <t>31_gas_8h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8h_percentage</t>
+  </si>
+  <si>
+    <t>31_v8_push_back_ml</t>
+  </si>
+  <si>
+    <t>31_time_24h</t>
+  </si>
+  <si>
+    <t>31_gas_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_24h_percentage</t>
+  </si>
+  <si>
+    <t>31_remarks_1</t>
+  </si>
+  <si>
+    <t>31_gp_8h_ml</t>
+  </si>
+  <si>
+    <t>31_gp_8_24_ml</t>
+  </si>
+  <si>
+    <t>31_net_gas_8h_ml</t>
+  </si>
+  <si>
+    <t>31_net_gas_8_24h_ml2</t>
+  </si>
+  <si>
+    <t>31_net_gas_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_24h_ml</t>
+  </si>
+  <si>
+    <t>31_gas_ml_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_percentage_dmd_truly_digestibility</t>
+  </si>
+  <si>
+    <t>31_part_fact</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_in_gas_8h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_in_gas_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_dmd_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_ndf_digested_in_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_g_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_g_g_dmd_24h</t>
+  </si>
+  <si>
+    <t>Sample weight, g</t>
+  </si>
+  <si>
+    <t>DM Incubated, mg</t>
+  </si>
+  <si>
+    <t>Time 0h</t>
+  </si>
+  <si>
+    <t>Gas 0h, ml</t>
+  </si>
+  <si>
+    <t>Time 8h</t>
+  </si>
+  <si>
+    <t>Gas 8h, ml</t>
+  </si>
+  <si>
+    <t>V8 Push back, ml</t>
+  </si>
+  <si>
+    <t>Time 24h</t>
+  </si>
+  <si>
+    <t>Gas 24h, ml</t>
+  </si>
+  <si>
+    <t>GP 8h, ml</t>
+  </si>
+  <si>
+    <t>GP 8-24h, ml</t>
+  </si>
+  <si>
+    <t>Net gas 8-24h, ml2</t>
+  </si>
+  <si>
+    <t>CH4 8h, ml</t>
+  </si>
+  <si>
+    <t>CH4 8-24h, ml</t>
+  </si>
+  <si>
+    <t>CH4 24h, ml</t>
+  </si>
+  <si>
+    <t>CH4 ml in gas, h8</t>
+  </si>
+  <si>
+    <t>CH4 ml in gas, 24h</t>
+  </si>
+  <si>
+    <t>31_gas_prod</t>
   </si>
 </sst>
 </file>
@@ -422,6 +707,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -687,15 +976,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AU24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -739,7 +1028,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -783,12 +1072,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -853,7 +1142,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -915,12 +1204,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1012,7 +1301,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1102,6 +1391,426 @@
       </c>
       <c r="AD14" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" t="s">
+        <v>124</v>
+      </c>
+      <c r="K18" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" t="s">
+        <v>127</v>
+      </c>
+      <c r="N18" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" t="s">
+        <v>129</v>
+      </c>
+      <c r="P18" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>131</v>
+      </c>
+      <c r="R18" t="s">
+        <v>132</v>
+      </c>
+      <c r="S18" t="s">
+        <v>133</v>
+      </c>
+      <c r="T18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" t="s">
+        <v>139</v>
+      </c>
+      <c r="O19" t="s">
+        <v>140</v>
+      </c>
+      <c r="P19" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>141</v>
+      </c>
+      <c r="R19" t="s">
+        <v>142</v>
+      </c>
+      <c r="S19" t="s">
+        <v>143</v>
+      </c>
+      <c r="T19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" t="s">
+        <v>151</v>
+      </c>
+      <c r="H23" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" t="s">
+        <v>154</v>
+      </c>
+      <c r="K23" t="s">
+        <v>155</v>
+      </c>
+      <c r="L23" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" t="s">
+        <v>157</v>
+      </c>
+      <c r="N23" t="s">
+        <v>158</v>
+      </c>
+      <c r="O23" t="s">
+        <v>159</v>
+      </c>
+      <c r="P23" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>161</v>
+      </c>
+      <c r="R23" t="s">
+        <v>162</v>
+      </c>
+      <c r="S23" t="s">
+        <v>163</v>
+      </c>
+      <c r="T23" t="s">
+        <v>164</v>
+      </c>
+      <c r="U23" t="s">
+        <v>165</v>
+      </c>
+      <c r="V23" t="s">
+        <v>166</v>
+      </c>
+      <c r="W23" t="s">
+        <v>167</v>
+      </c>
+      <c r="X23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>176</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>181</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>182</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>185</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>186</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>188</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>189</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>190</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" t="s">
+        <v>58</v>
+      </c>
+      <c r="J24" t="s">
+        <v>59</v>
+      </c>
+      <c r="K24" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>95</v>
+      </c>
+      <c r="N24" t="s">
+        <v>96</v>
+      </c>
+      <c r="O24" t="s">
+        <v>97</v>
+      </c>
+      <c r="P24" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>192</v>
+      </c>
+      <c r="R24" t="s">
+        <v>193</v>
+      </c>
+      <c r="S24" t="s">
+        <v>140</v>
+      </c>
+      <c r="T24" t="s">
+        <v>194</v>
+      </c>
+      <c r="U24" t="s">
+        <v>195</v>
+      </c>
+      <c r="V24" t="s">
+        <v>196</v>
+      </c>
+      <c r="W24" t="s">
+        <v>197</v>
+      </c>
+      <c r="X24" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>204</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>208</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
